--- a/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-bf.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-bf.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4884" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4884" uniqueCount="608">
   <si>
     <t>Property</t>
   </si>
@@ -1605,6 +1605,17 @@
   </si>
   <si>
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;code value="component:&amp;lt;slice&amp;gt;.code"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:code}
+</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -11172,7 +11183,7 @@
         <v>76</v>
       </c>
       <c r="S87" t="s" s="2">
-        <v>76</v>
+        <v>503</v>
       </c>
       <c r="T87" t="s" s="2">
         <v>76</v>
@@ -11199,7 +11210,7 @@
         <v>76</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>223</v>
+        <v>504</v>
       </c>
       <c r="AC87" s="2"/>
       <c r="AD87" t="s" s="2">
@@ -11221,15 +11232,15 @@
         <v>90</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11326,10 +11337,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11428,10 +11439,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11532,10 +11543,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11561,13 +11572,13 @@
         <v>216</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="O91" t="s" s="2">
         <v>233</v>
@@ -11619,7 +11630,7 @@
         <v>76</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
@@ -11636,10 +11647,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11662,16 +11673,16 @@
         <v>84</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M92" t="s" s="2">
         <v>349</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="O92" t="s" s="2">
         <v>342</v>
@@ -11721,7 +11732,7 @@
         <v>110</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>74</v>
@@ -11738,10 +11749,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C93" t="s" s="2">
         <v>347</v>
@@ -11769,13 +11780,13 @@
         <v>338</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M93" t="s" s="2">
         <v>349</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="O93" t="s" s="2">
         <v>342</v>
@@ -11827,7 +11838,7 @@
         <v>76</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>74</v>
@@ -11844,10 +11855,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11944,10 +11955,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12046,10 +12057,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12150,10 +12161,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12256,10 +12267,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12360,10 +12371,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12464,10 +12475,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12568,10 +12579,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12597,13 +12608,13 @@
         <v>216</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="O101" t="s" s="2">
         <v>399</v>
@@ -12655,7 +12666,7 @@
         <v>76</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>74</v>
@@ -12672,10 +12683,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12701,10 +12712,10 @@
         <v>216</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>407</v>
@@ -12759,7 +12770,7 @@
         <v>76</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>74</v>
@@ -12776,10 +12787,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12805,10 +12816,10 @@
         <v>77</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="N103" t="s" s="2">
         <v>444</v>
@@ -12863,7 +12874,7 @@
         <v>76</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>74</v>
@@ -12880,13 +12891,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>498</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>76</v>
@@ -12911,10 +12922,10 @@
         <v>441</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="N104" t="s" s="2">
         <v>501</v>
@@ -12981,15 +12992,15 @@
         <v>90</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13086,10 +13097,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13188,10 +13199,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13292,10 +13303,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13321,13 +13332,13 @@
         <v>216</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="O108" t="s" s="2">
         <v>233</v>
@@ -13379,7 +13390,7 @@
         <v>76</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>83</v>
@@ -13396,10 +13407,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13496,10 +13507,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13598,10 +13609,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13673,7 +13684,7 @@
         <v>76</v>
       </c>
       <c r="AB111" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AC111" s="2"/>
       <c r="AD111" t="s" s="2">
@@ -13700,13 +13711,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="B112" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="B112" t="s" s="2">
-        <v>553</v>
-      </c>
       <c r="C112" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>76</v>
@@ -13731,10 +13742,10 @@
         <v>137</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>241</v>
@@ -13769,7 +13780,7 @@
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>76</v>
@@ -13804,10 +13815,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C113" t="s" s="2">
         <v>276</v>
@@ -13835,10 +13846,10 @@
         <v>137</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>241</v>
@@ -13873,7 +13884,7 @@
       </c>
       <c r="Y113" s="2"/>
       <c r="Z113" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>76</v>
@@ -13908,10 +13919,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14012,10 +14023,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14038,16 +14049,16 @@
         <v>84</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M115" t="s" s="2">
         <v>349</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="O115" t="s" s="2">
         <v>342</v>
@@ -14097,7 +14108,7 @@
         <v>344</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>74</v>
@@ -14114,10 +14125,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C116" t="s" s="2">
         <v>347</v>
@@ -14145,13 +14156,13 @@
         <v>338</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M116" t="s" s="2">
         <v>349</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="O116" t="s" s="2">
         <v>342</v>
@@ -14203,7 +14214,7 @@
         <v>76</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>74</v>
@@ -14220,10 +14231,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14320,10 +14331,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14422,10 +14433,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14526,10 +14537,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14632,10 +14643,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14680,7 +14691,7 @@
         <v>76</v>
       </c>
       <c r="S121" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="T121" t="s" s="2">
         <v>76</v>
@@ -14736,10 +14747,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14840,10 +14851,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14888,7 +14899,7 @@
         <v>76</v>
       </c>
       <c r="S123" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="T123" t="s" s="2">
         <v>76</v>
@@ -14944,10 +14955,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14973,13 +14984,13 @@
         <v>216</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="O124" t="s" s="2">
         <v>399</v>
@@ -15031,7 +15042,7 @@
         <v>76</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>74</v>
@@ -15048,10 +15059,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15077,10 +15088,10 @@
         <v>216</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="N125" t="s" s="2">
         <v>407</v>
@@ -15135,7 +15146,7 @@
         <v>76</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>74</v>
@@ -15152,10 +15163,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15181,10 +15192,10 @@
         <v>77</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="N126" t="s" s="2">
         <v>444</v>
@@ -15239,7 +15250,7 @@
         <v>76</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>74</v>
@@ -15256,13 +15267,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>498</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="D127" t="s" s="2">
         <v>76</v>
@@ -15287,10 +15298,10 @@
         <v>441</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N127" t="s" s="2">
         <v>501</v>
@@ -15357,15 +15368,15 @@
         <v>90</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15462,10 +15473,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15564,10 +15575,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15668,10 +15679,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15697,13 +15708,13 @@
         <v>216</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="O131" t="s" s="2">
         <v>233</v>
@@ -15755,7 +15766,7 @@
         <v>76</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>83</v>
@@ -15772,10 +15783,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15872,10 +15883,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15974,10 +15985,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16049,7 +16060,7 @@
         <v>76</v>
       </c>
       <c r="AB134" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AC134" s="2"/>
       <c r="AD134" t="s" s="2">
@@ -16076,13 +16087,13 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D135" t="s" s="2">
         <v>76</v>
@@ -16107,10 +16118,10 @@
         <v>137</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="N135" t="s" s="2">
         <v>241</v>
@@ -16145,7 +16156,7 @@
       </c>
       <c r="Y135" s="2"/>
       <c r="Z135" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>76</v>
@@ -16180,10 +16191,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C136" t="s" s="2">
         <v>276</v>
@@ -16211,10 +16222,10 @@
         <v>137</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="N136" t="s" s="2">
         <v>241</v>
@@ -16249,7 +16260,7 @@
       </c>
       <c r="Y136" s="2"/>
       <c r="Z136" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>76</v>
@@ -16284,10 +16295,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16388,10 +16399,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16414,16 +16425,16 @@
         <v>84</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M138" t="s" s="2">
         <v>349</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="O138" t="s" s="2">
         <v>342</v>
@@ -16473,7 +16484,7 @@
         <v>344</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>74</v>
@@ -16490,10 +16501,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C139" t="s" s="2">
         <v>347</v>
@@ -16521,13 +16532,13 @@
         <v>338</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M139" t="s" s="2">
         <v>349</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="O139" t="s" s="2">
         <v>342</v>
@@ -16579,7 +16590,7 @@
         <v>76</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>74</v>
@@ -16596,10 +16607,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16696,10 +16707,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16798,10 +16809,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16902,10 +16913,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -17008,10 +17019,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17056,7 +17067,7 @@
         <v>76</v>
       </c>
       <c r="S144" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="T144" t="s" s="2">
         <v>76</v>
@@ -17112,10 +17123,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17216,10 +17227,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17264,7 +17275,7 @@
         <v>76</v>
       </c>
       <c r="S146" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="T146" t="s" s="2">
         <v>76</v>
@@ -17320,10 +17331,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17349,13 +17360,13 @@
         <v>216</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="O147" t="s" s="2">
         <v>399</v>
@@ -17407,7 +17418,7 @@
         <v>76</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>74</v>
@@ -17424,10 +17435,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17453,10 +17464,10 @@
         <v>216</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="N148" t="s" s="2">
         <v>407</v>
@@ -17511,7 +17522,7 @@
         <v>76</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>74</v>
@@ -17528,10 +17539,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17557,10 +17568,10 @@
         <v>77</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="N149" t="s" s="2">
         <v>444</v>
@@ -17615,7 +17626,7 @@
         <v>76</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>74</v>

--- a/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-bf.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-bf.xlsx
@@ -1832,7 +1832,7 @@
     <t>Observation.component:predicted.value[x]:valueQuantity.unit</t>
   </si>
   <si>
-    <t>L</t>
+    <t>/min</t>
   </si>
   <si>
     <t>Observation.component:predicted.value[x]:valueQuantity.system</t>
